--- a/template-pricetag.xlsx
+++ b/template-pricetag.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="12">
   <si>
     <t>Item</t>
   </si>
@@ -36,7 +36,19 @@
     <t>Deskripsi</t>
   </si>
   <si>
-    <t>Gambar</t>
+    <t>Gambar 1</t>
+  </si>
+  <si>
+    <t>Gambar 2</t>
+  </si>
+  <si>
+    <t>Gambar 3</t>
+  </si>
+  <si>
+    <t>Gambar 4</t>
+  </si>
+  <si>
+    <t>Gambar 5</t>
   </si>
 </sst>
 </file>
@@ -408,6 +420,18 @@
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6"/>
@@ -1907,6 +1931,18 @@
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6"/>
@@ -1915,6 +1951,7 @@
       <c r="D2" s="7"/>
       <c r="E2" s="8"/>
       <c r="F2" s="9"/>
+      <c r="G2" s="10"/>
     </row>
     <row r="3">
       <c r="A3" s="7"/>
@@ -6755,15 +6792,27 @@
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="12"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="10"/>
     </row>
     <row r="3">
       <c r="A3" s="10"/>

--- a/template-pricetag.xlsx
+++ b/template-pricetag.xlsx
@@ -59,7 +59,8 @@
         <color rgb="FF000000"/>
         <sz val="11.0"/>
       </rPr>
-      <t>Ketentuan Header :</t>
+      <t xml:space="preserve">Ketentuan Header :
+</t>
     </r>
     <r>
       <rPr>
@@ -67,8 +68,7 @@
         <color rgb="FF000000"/>
         <sz val="11.0"/>
       </rPr>
-      <t xml:space="preserve">
-- Header berwarna merah WAJIB diisi.
+      <t>- Header berwarna merah WAJIB diisi.
 - Pastikan semua kolom dengan header merah tidak boleh kosong.</t>
     </r>
   </si>
@@ -11813,40 +11813,73 @@
     </row>
     <row r="6">
       <c r="A6" s="28"/>
+      <c r="B6" s="28"/>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
       <c r="E6" s="22"/>
       <c r="F6" s="22"/>
       <c r="G6" s="13"/>
       <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
     </row>
     <row r="7">
+      <c r="A7" s="28"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
       <c r="G7" s="13"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
     </row>
     <row r="8">
+      <c r="A8" s="28"/>
+      <c r="B8" s="28"/>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="13"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
     </row>
     <row r="9">
+      <c r="A9" s="28"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
       <c r="G9" s="13"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
     </row>
     <row r="10">
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
       <c r="E10" s="22"/>
       <c r="F10" s="22"/>
       <c r="G10" s="13"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
     </row>
     <row r="11">
       <c r="A11" s="14"/>
@@ -16574,10 +16607,6 @@
       <c r="F1000" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A6:B10"/>
-    <mergeCell ref="H6:L10"/>
-  </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>